--- a/data-raw/data-tidy/public-site/moa-machine-county/xlsx/case-year-2025-batch05.xlsx
+++ b/data-raw/data-tidy/public-site/moa-machine-county/xlsx/case-year-2025-batch05.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">盐湖</t>
   </si>
   <si>
-    <t xml:space="preserve">丹霞红梨</t>
+    <t xml:space="preserve">红梨</t>
   </si>
   <si>
     <t xml:space="preserve">山西临猗大卫嘎啦苹果机械化生产模式与典型案例</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">临猗</t>
   </si>
   <si>
-    <t xml:space="preserve">大卫嘎啦苹果</t>
+    <t xml:space="preserve">苹果</t>
   </si>
   <si>
     <t xml:space="preserve">甘肃礼县矮砧密植苹果机械化智能化生产模式与典型案例</t>
@@ -98,9 +98,6 @@
     <t xml:space="preserve">礼县</t>
   </si>
   <si>
-    <t xml:space="preserve">苹果</t>
-  </si>
-  <si>
     <t xml:space="preserve">江西金溪翠冠梨新型棚架机械化生产模式与典型案例</t>
   </si>
   <si>
@@ -110,7 +107,7 @@
     <t xml:space="preserve">金溪</t>
   </si>
   <si>
-    <t xml:space="preserve">翠冠梨</t>
+    <t xml:space="preserve">梨</t>
   </si>
   <si>
     <t xml:space="preserve">江西新余蜜桔机械化生产模式与典型案例</t>
@@ -146,9 +143,6 @@
     <t xml:space="preserve">金沙</t>
   </si>
   <si>
-    <t xml:space="preserve">碾茶</t>
-  </si>
-  <si>
     <t xml:space="preserve">贵州荔波茶园机械化生产模式与典型案例</t>
   </si>
   <si>
@@ -164,9 +158,6 @@
     <t xml:space="preserve">安溪</t>
   </si>
   <si>
-    <t xml:space="preserve">铁观音</t>
-  </si>
-  <si>
     <t xml:space="preserve">江苏仪征绿杨春茶叶机械化生产模式与典型案例</t>
   </si>
   <si>
@@ -176,9 +167,6 @@
     <t xml:space="preserve">仪征</t>
   </si>
   <si>
-    <t xml:space="preserve">绿杨春</t>
-  </si>
-  <si>
     <t xml:space="preserve">浙江杭州桐庐龙井茶叶机械化生产模式与典型案例</t>
   </si>
   <si>
@@ -188,9 +176,6 @@
     <t xml:space="preserve">桐庐</t>
   </si>
   <si>
-    <t xml:space="preserve">龙井</t>
-  </si>
-  <si>
     <t xml:space="preserve">中药材</t>
   </si>
   <si>
@@ -209,7 +194,7 @@
     <t xml:space="preserve">陵川</t>
   </si>
   <si>
-    <t xml:space="preserve">潞党参</t>
+    <t xml:space="preserve">党参</t>
   </si>
   <si>
     <t xml:space="preserve">山西盐湖丹参机械化生产模式与典型案例</t>
@@ -755,7 +740,7 @@
         <v>27</v>
       </c>
       <c r="I7" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -775,16 +760,16 @@
         <v>4</v>
       </c>
       <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
         <v>29</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>30</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>31</v>
-      </c>
-      <c r="I8" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -804,16 +789,16 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
         <v>33</v>
       </c>
-      <c r="G9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>34</v>
-      </c>
-      <c r="I9" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -833,16 +818,16 @@
         <v>6</v>
       </c>
       <c r="F10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" t="s">
         <v>36</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>37</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>38</v>
-      </c>
-      <c r="I10" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -853,7 +838,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -862,16 +847,16 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" t="s">
         <v>41</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>42</v>
       </c>
-      <c r="H11" t="s">
-        <v>43</v>
-      </c>
       <c r="I11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
@@ -882,7 +867,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -891,16 +876,16 @@
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -911,7 +896,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
@@ -920,16 +905,16 @@
         <v>3</v>
       </c>
       <c r="F13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" t="s">
         <v>47</v>
       </c>
-      <c r="G13" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" t="s">
-        <v>49</v>
-      </c>
       <c r="I13" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -940,7 +925,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
         <v>13</v>
@@ -949,16 +934,16 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I14" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -969,7 +954,7 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
@@ -978,16 +963,16 @@
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G15" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H15" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I15" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
@@ -998,7 +983,7 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
@@ -1007,16 +992,16 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G16" t="s">
         <v>26</v>
       </c>
       <c r="H16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
@@ -1027,7 +1012,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D17" t="n">
         <v>16</v>
@@ -1036,16 +1021,16 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G17" t="s">
         <v>19</v>
       </c>
       <c r="H17" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="I17" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -1056,7 +1041,7 @@
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>17</v>
@@ -1065,7 +1050,7 @@
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G18" t="s">
         <v>19</v>
@@ -1074,7 +1059,7 @@
         <v>20</v>
       </c>
       <c r="I18" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -1085,7 +1070,7 @@
         <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D19" t="n">
         <v>18</v>
@@ -1094,16 +1079,16 @@
         <v>4</v>
       </c>
       <c r="F19" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G19" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H19" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I19" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
@@ -1114,7 +1099,7 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
         <v>19</v>
@@ -1123,14 +1108,14 @@
         <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H20"/>
       <c r="I20" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
